--- a/Stock Investing (XTB)/Data/EUR.xlsx
+++ b/Stock Investing (XTB)/Data/EUR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szkod\Desktop\Projekty\Power BI\Stock Investing (XTB)\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB14F2B7-5854-4AEA-A637-BFD6A14C8E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353290A0-0CD6-4F38-995A-BFF01B7E49F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Closed Positions" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="55">
   <si>
     <t>Account</t>
   </si>
@@ -589,7 +589,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.453125" bestFit="1" customWidth="1"/>
@@ -744,16 +744,16 @@
         <v>1205.2</v>
       </c>
       <c r="I6" s="2">
-        <v>46096.336875000001</v>
+        <v>46110.336875000001</v>
       </c>
       <c r="J6" t="s">
         <v>34</v>
       </c>
       <c r="K6">
-        <v>8.85</v>
+        <v>50</v>
       </c>
       <c r="L6">
-        <v>8.85</v>
+        <v>50</v>
       </c>
       <c r="M6">
         <v>148.71</v>
@@ -797,46 +797,46 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
       </c>
       <c r="E7">
-        <v>0.5857</v>
+        <v>0.12989999999999999</v>
       </c>
       <c r="F7">
-        <v>588.74</v>
+        <v>1144.8</v>
       </c>
       <c r="G7" s="2">
         <v>45902.295717592591</v>
       </c>
       <c r="H7">
-        <v>626.28</v>
+        <v>1205.2</v>
       </c>
       <c r="I7" s="2">
-        <v>46077.336875000001</v>
+        <v>46096.336875000001</v>
       </c>
       <c r="J7" t="s">
         <v>34</v>
       </c>
       <c r="K7">
-        <v>22.98</v>
+        <v>8.85</v>
       </c>
       <c r="L7">
-        <v>22.98</v>
+        <v>8.85</v>
       </c>
       <c r="M7">
-        <v>344.83</v>
+        <v>148.71</v>
       </c>
       <c r="N7">
-        <v>366.81</v>
+        <v>156.56</v>
       </c>
       <c r="O7" t="s">
         <v>2</v>
@@ -874,46 +874,46 @@
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
       </c>
       <c r="E8">
-        <v>2.41E-2</v>
+        <v>0.5857</v>
       </c>
       <c r="F8">
-        <v>83.31</v>
+        <v>588.74</v>
       </c>
       <c r="G8" s="2">
-        <v>45837.294641203705</v>
+        <v>45902.295717592591</v>
       </c>
       <c r="H8">
-        <v>95.68</v>
+        <v>626.28</v>
       </c>
       <c r="I8" s="2">
-        <v>46076.336867048609</v>
+        <v>46077.336875000001</v>
       </c>
       <c r="J8" t="s">
         <v>34</v>
       </c>
       <c r="K8">
-        <v>0.3</v>
+        <v>22.98</v>
       </c>
       <c r="L8">
-        <v>0.3</v>
+        <v>22.98</v>
       </c>
       <c r="M8">
-        <v>2.0099999999999998</v>
+        <v>344.83</v>
       </c>
       <c r="N8">
-        <v>2.31</v>
+        <v>366.81</v>
       </c>
       <c r="O8" t="s">
         <v>2</v>
@@ -951,46 +951,46 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
       </c>
       <c r="E9">
-        <v>0.65310000000000001</v>
+        <v>2.41E-2</v>
       </c>
       <c r="F9">
-        <v>636.58000000000004</v>
+        <v>83.31</v>
       </c>
       <c r="G9" s="2">
-        <v>46035.614004629628</v>
+        <v>45837.294641203705</v>
       </c>
       <c r="H9">
-        <v>623.76</v>
+        <v>95.68</v>
       </c>
       <c r="I9" s="2">
-        <v>46075.336863425924</v>
+        <v>46076.336867048609</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
       </c>
       <c r="K9">
-        <v>-9.3699999999999992</v>
+        <v>0.3</v>
       </c>
       <c r="L9">
-        <v>-9.3699999999999992</v>
+        <v>0.3</v>
       </c>
       <c r="M9">
-        <v>415.75</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="N9">
-        <v>407.38</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="s">
         <v>2</v>
@@ -1040,34 +1040,34 @@
         <v>33</v>
       </c>
       <c r="E10">
-        <v>1.23E-2</v>
+        <v>0.65310000000000001</v>
       </c>
       <c r="F10">
-        <v>627.44000000000005</v>
+        <v>636.58000000000004</v>
       </c>
       <c r="G10" s="2">
-        <v>46019.336793981478</v>
+        <v>46035.614004629628</v>
       </c>
       <c r="H10">
         <v>623.76</v>
       </c>
       <c r="I10" s="2">
-        <v>46074.336863425924</v>
+        <v>46075.336863425924</v>
       </c>
       <c r="J10" t="s">
         <v>34</v>
       </c>
       <c r="K10">
-        <v>-0.05</v>
+        <v>-9.3699999999999992</v>
       </c>
       <c r="L10">
-        <v>-0.05</v>
+        <v>-9.3699999999999992</v>
       </c>
       <c r="M10">
-        <v>7.72</v>
+        <v>415.75</v>
       </c>
       <c r="N10">
-        <v>7.67</v>
+        <v>407.38</v>
       </c>
       <c r="O10" t="s">
         <v>2</v>
@@ -1117,34 +1117,34 @@
         <v>33</v>
       </c>
       <c r="E11">
-        <v>0.2747</v>
+        <v>1.23E-2</v>
       </c>
       <c r="F11">
-        <v>622.6</v>
+        <v>627.44000000000005</v>
       </c>
       <c r="G11" s="2">
-        <v>46007.337372685186</v>
+        <v>46019.336793981478</v>
       </c>
       <c r="H11">
         <v>623.76</v>
       </c>
       <c r="I11" s="2">
-        <v>46073.336863425924</v>
+        <v>46074.336863425924</v>
       </c>
       <c r="J11" t="s">
         <v>34</v>
       </c>
       <c r="K11">
-        <v>0.35</v>
+        <v>-0.05</v>
       </c>
       <c r="L11">
-        <v>0.35</v>
+        <v>-0.05</v>
       </c>
       <c r="M11">
-        <v>171.03</v>
+        <v>7.72</v>
       </c>
       <c r="N11">
-        <v>171.35</v>
+        <v>7.67</v>
       </c>
       <c r="O11" t="s">
         <v>2</v>
@@ -1182,15 +1182,92 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>0.2747</v>
+      </c>
+      <c r="F12">
+        <v>622.6</v>
+      </c>
+      <c r="G12" s="2">
+        <v>46007.337372685186</v>
+      </c>
+      <c r="H12">
+        <v>623.76</v>
+      </c>
+      <c r="I12" s="2">
+        <v>46073.336863425924</v>
+      </c>
+      <c r="J12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12">
+        <v>0.35</v>
+      </c>
+      <c r="L12">
+        <v>0.35</v>
+      </c>
+      <c r="M12">
+        <v>171.03</v>
+      </c>
+      <c r="N12">
+        <v>171.35</v>
+      </c>
+      <c r="O12" t="s">
+        <v>2</v>
+      </c>
+      <c r="P12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>2</v>
+      </c>
+      <c r="S12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T12" t="s">
+        <v>2</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12" t="s">
+        <v>35</v>
+      </c>
+      <c r="X12" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="3">
-        <f>SUM(K6:K11)</f>
-        <v>23.06</v>
-      </c>
-      <c r="L12" s="3">
-        <f>SUM(L6:L11)</f>
-        <v>23.06</v>
+      <c r="K13" s="3">
+        <f>SUM(K6:K12)</f>
+        <v>73.059999999999988</v>
+      </c>
+      <c r="L13" s="3">
+        <f>SUM(L6:L12)</f>
+        <v>73.059999999999988</v>
       </c>
     </row>
   </sheetData>
@@ -1204,7 +1281,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.453125" bestFit="1" customWidth="1"/>
@@ -1352,7 +1429,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
@@ -1361,10 +1438,10 @@
         <v>2</v>
       </c>
       <c r="D9" s="4">
-        <v>46084.012696759259</v>
+        <v>46085.33871527778</v>
       </c>
       <c r="E9">
-        <v>-0.04</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
@@ -1378,19 +1455,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D10" s="4">
-        <v>46078.336655092593</v>
+        <v>46084.33871527778</v>
       </c>
       <c r="E10">
-        <v>-790.52</v>
+        <v>100</v>
       </c>
       <c r="F10" t="s">
         <v>53</v>
@@ -1399,24 +1476,24 @@
         <v>53</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="D11" s="4">
-        <v>46078.336643518516</v>
+        <v>46084.012696759259</v>
       </c>
       <c r="E11">
-        <v>-3080.28</v>
+        <v>-0.04</v>
       </c>
       <c r="F11" t="s">
         <v>53</v>
@@ -1425,7 +1502,7 @@
         <v>53</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1433,16 +1510,16 @@
         <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4">
-        <v>46078.336643518516</v>
+        <v>46078.336655092593</v>
       </c>
       <c r="E12">
-        <v>-69.400000000000006</v>
+        <v>-790.52</v>
       </c>
       <c r="F12" t="s">
         <v>53</v>
@@ -1459,16 +1536,16 @@
         <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D13" s="4">
         <v>46078.336643518516</v>
       </c>
       <c r="E13">
-        <v>-3.1</v>
+        <v>-3080.28</v>
       </c>
       <c r="F13" t="s">
         <v>53</v>
@@ -1482,19 +1559,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" s="4">
-        <v>46078.337199074071</v>
+        <v>46078.336643518516</v>
       </c>
       <c r="E14">
-        <v>4100</v>
+        <v>-69.400000000000006</v>
       </c>
       <c r="F14" t="s">
         <v>53</v>
@@ -1508,19 +1585,19 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D15" s="4">
-        <v>46077.818333333336</v>
+        <v>46078.336643518516</v>
       </c>
       <c r="E15">
-        <v>4000</v>
+        <v>-3.1</v>
       </c>
       <c r="F15" t="s">
         <v>53</v>
@@ -1534,19 +1611,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D16" s="4">
-        <v>46077.818333333336</v>
+        <v>46078.337199074071</v>
       </c>
       <c r="E16">
-        <v>-4000</v>
+        <v>4100</v>
       </c>
       <c r="F16" t="s">
         <v>53</v>
@@ -1555,7 +1632,7 @@
         <v>53</v>
       </c>
       <c r="H16" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1569,10 +1646,10 @@
         <v>2</v>
       </c>
       <c r="D17" s="4">
-        <v>46077.33871527778</v>
+        <v>46077.818333333336</v>
       </c>
       <c r="E17">
-        <v>-4000</v>
+        <v>4000</v>
       </c>
       <c r="F17" t="s">
         <v>53</v>
@@ -1595,10 +1672,10 @@
         <v>2</v>
       </c>
       <c r="D18" s="4">
-        <v>46077.33871527778</v>
+        <v>46077.818333333336</v>
       </c>
       <c r="E18">
-        <v>4000</v>
+        <v>-4000</v>
       </c>
       <c r="F18" t="s">
         <v>53</v>
@@ -1624,7 +1701,7 @@
         <v>46077.33871527778</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>-4000</v>
       </c>
       <c r="F19" t="s">
         <v>53</v>
@@ -1633,16 +1710,68 @@
         <v>53</v>
       </c>
       <c r="H19" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4">
+        <v>46077.33871527778</v>
+      </c>
+      <c r="E20">
+        <v>4000</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4">
+        <v>46077.33871527778</v>
+      </c>
+      <c r="E21">
+        <v>1000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="3">
-        <f>SUM(E6:E19)</f>
-        <v>257.02000000000044</v>
+      <c r="E22" s="3">
+        <f>SUM(E6:E21)</f>
+        <v>1357.0200000000004</v>
       </c>
     </row>
   </sheetData>
